--- a/Team-Data/2014-15/12-30-2014-15.xlsx
+++ b/Team-Data/2014-15/12-30-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,91 +728,91 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.742</v>
+        <v>0.733</v>
       </c>
       <c r="H2" t="n">
         <v>48.3</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O2" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P2" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
         <v>8.4</v>
       </c>
       <c r="S2" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
         <v>14.7</v>
       </c>
       <c r="W2" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X2" t="n">
         <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z2" t="n">
         <v>18.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.2</v>
+        <v>101.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG2" t="n">
         <v>4</v>
@@ -760,13 +827,13 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>6</v>
@@ -775,10 +842,10 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -787,13 +854,13 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -802,7 +869,7 @@
         <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -811,10 +878,10 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -924,7 +991,7 @@
         <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
         <v>18</v>
@@ -933,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
         <v>3</v>
@@ -942,28 +1009,28 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN3" t="n">
         <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
         <v>8</v>
@@ -975,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.484</v>
+        <v>0.467</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
         <v>36.4</v>
       </c>
       <c r="J4" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
@@ -1052,70 +1119,70 @@
         <v>7.1</v>
       </c>
       <c r="M4" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.338</v>
+        <v>0.336</v>
       </c>
       <c r="O4" t="n">
         <v>16.9</v>
       </c>
       <c r="P4" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="R4" t="n">
         <v>9.9</v>
       </c>
       <c r="S4" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U4" t="n">
         <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB4" t="n">
         <v>96.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.8</v>
+        <v>-2.3</v>
       </c>
       <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
         <v>17</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>15</v>
       </c>
       <c r="AF4" t="n">
         <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
@@ -1127,58 +1194,58 @@
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
         <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-4.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1303,7 +1370,7 @@
         <v>23</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1324,7 +1391,7 @@
         <v>21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
         <v>26</v>
@@ -1333,7 +1400,7 @@
         <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU5" t="n">
         <v>23</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY5" t="n">
         <v>18</v>
@@ -1354,13 +1421,13 @@
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -1389,67 +1456,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
         <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="L6" t="n">
         <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O6" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="P6" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.777</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
         <v>11.3</v>
       </c>
       <c r="S6" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T6" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="U6" t="n">
         <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W6" t="n">
         <v>5.8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="Y6" t="n">
         <v>5</v>
@@ -1458,43 +1525,43 @@
         <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.5</v>
+        <v>103.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" t="n">
         <v>7</v>
       </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ6" t="n">
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AN6" t="n">
         <v>10</v>
@@ -1506,7 +1573,7 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AR6" t="n">
         <v>10</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1536,13 +1603,13 @@
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
         <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.581</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1589,34 +1656,34 @@
         <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L7" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="O7" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P7" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R7" t="n">
         <v>10.5</v>
       </c>
       <c r="S7" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T7" t="n">
         <v>40.8</v>
@@ -1625,34 +1692,34 @@
         <v>22.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y7" t="n">
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB7" t="n">
         <v>102.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,28 +1728,28 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL7" t="n">
         <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
         <v>7</v>
@@ -1691,13 +1758,13 @@
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
@@ -1706,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>23</v>
@@ -1718,10 +1785,10 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -1756,94 +1823,94 @@
         <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.719</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L8" t="n">
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.355</v>
+        <v>0.352</v>
       </c>
       <c r="O8" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P8" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.766</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
         <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W8" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.9</v>
+        <v>109.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1858,19 +1925,19 @@
         <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP8" t="n">
         <v>15</v>
       </c>
-      <c r="AO8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
@@ -1879,16 +1946,16 @@
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -1900,7 +1967,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
         <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.406</v>
+        <v>0.419</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1962,40 +2029,40 @@
         <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
         <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.738</v>
+        <v>0.741</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S9" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="U9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y9" t="n">
         <v>5.8</v>
@@ -2010,25 +2077,25 @@
         <v>101.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
         <v>3</v>
@@ -2049,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
@@ -2067,16 +2134,16 @@
         <v>19</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -2117,85 +2184,85 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.258</v>
+        <v>0.233</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J10" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.42</v>
+        <v>0.419</v>
       </c>
       <c r="L10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.345</v>
+        <v>0.341</v>
       </c>
       <c r="O10" t="n">
         <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.676</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W10" t="n">
         <v>7.3</v>
       </c>
       <c r="X10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
         <v>20.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>96</v>
+        <v>95.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.3</v>
+        <v>-5.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
@@ -2207,10 +2274,10 @@
         <v>27</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
         <v>7</v>
@@ -2219,13 +2286,13 @@
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
@@ -2240,13 +2307,13 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
         <v>21</v>
@@ -2267,10 +2334,10 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.833</v>
+        <v>0.828</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="J11" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.482</v>
+        <v>0.479</v>
       </c>
       <c r="L11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O11" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P11" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R11" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
         <v>35.2</v>
       </c>
       <c r="T11" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U11" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="V11" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X11" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z11" t="n">
         <v>20.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>108.1</v>
+        <v>107.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2404,7 +2471,7 @@
         <v>5</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
@@ -2413,19 +2480,19 @@
         <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2434,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J12" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.43</v>
@@ -2508,70 +2575,70 @@
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>25.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.709</v>
+        <v>0.707</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U12" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="W12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.7</v>
+        <v>101</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
         <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
@@ -2589,28 +2656,28 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,22 +2686,22 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2768,10 +2835,10 @@
         <v>21</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2783,16 +2850,16 @@
         <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2801,7 +2868,7 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
@@ -2816,7 +2883,7 @@
         <v>28</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>5.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>9</v>
@@ -2959,22 +3026,22 @@
         <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
         <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
         <v>7</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -3030,97 +3097,97 @@
         <v>31</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.323</v>
+        <v>0.29</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="J15" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.366</v>
+        <v>0.357</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S15" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="T15" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB15" t="n">
-        <v>103</v>
+        <v>102.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
         <v>2</v>
@@ -3129,40 +3196,40 @@
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AM15" t="n">
         <v>21</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV15" t="n">
         <v>5</v>
       </c>
-      <c r="AS15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>6</v>
-      </c>
       <c r="AW15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3174,13 +3241,13 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.742</v>
+        <v>0.733</v>
       </c>
       <c r="H16" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I16" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J16" t="n">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L16" t="n">
         <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P16" t="n">
         <v>24</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
         <v>31.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
         <v>22.7</v>
       </c>
       <c r="V16" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
@@ -3275,25 +3342,25 @@
         <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>102.1</v>
+        <v>102.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>4</v>
@@ -3308,7 +3375,7 @@
         <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3320,13 +3387,13 @@
         <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
         <v>21</v>
@@ -3335,31 +3402,31 @@
         <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
         <v>25</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>13</v>
@@ -3499,10 +3566,10 @@
         <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3535,10 +3602,10 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>26</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3681,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ18" t="n">
         <v>7</v>
@@ -3696,10 +3763,10 @@
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU18" t="n">
         <v>11</v>
@@ -3708,25 +3775,25 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY18" t="n">
         <v>15</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>0.167</v>
+        <v>0.172</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3773,43 +3840,43 @@
         <v>37.2</v>
       </c>
       <c r="J19" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.338</v>
+        <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="P19" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0.72</v>
       </c>
       <c r="R19" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S19" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T19" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U19" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
         <v>9.1</v>
@@ -3818,22 +3885,22 @@
         <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-10.3</v>
+        <v>-10.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3851,7 +3918,7 @@
         <v>17</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3863,16 +3930,16 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3887,16 +3954,16 @@
         <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
       </c>
       <c r="AY19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
         <v>15</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -3955,88 +4022,88 @@
         <v>39.1</v>
       </c>
       <c r="J20" t="n">
-        <v>84.8</v>
+        <v>85.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.461</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.341</v>
+        <v>0.334</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.762</v>
+        <v>0.756</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>31.2</v>
       </c>
       <c r="T20" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>19.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.9</v>
+        <v>101.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4072,16 +4139,16 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4276,7 @@
         <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>22</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4251,10 +4318,10 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW21" t="n">
         <v>20</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>21</v>
       </c>
       <c r="AX21" t="n">
         <v>27</v>
@@ -4266,13 +4333,13 @@
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>27</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4388,7 +4455,7 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
         <v>22</v>
@@ -4397,7 +4464,7 @@
         <v>19</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -4415,7 +4482,7 @@
         <v>16</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
         <v>23</v>
@@ -4424,7 +4491,7 @@
         <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
         <v>2</v>
@@ -4433,13 +4500,13 @@
         <v>30</v>
       </c>
       <c r="AV22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
@@ -4454,7 +4521,7 @@
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -4498,40 +4565,40 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J23" t="n">
         <v>80.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.374</v>
+        <v>0.38</v>
       </c>
       <c r="O23" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="P23" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.722</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
         <v>19.9</v>
@@ -4543,22 +4610,22 @@
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB23" t="n">
         <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-4.9</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,16 +4643,16 @@
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
@@ -4600,34 +4667,34 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR23" t="n">
         <v>27</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU23" t="n">
         <v>28</v>
       </c>
-      <c r="AS23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>26</v>
-      </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>29</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,67 +4750,67 @@
         <v>33.3</v>
       </c>
       <c r="J24" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.411</v>
+        <v>0.412</v>
       </c>
       <c r="L24" t="n">
         <v>7.1</v>
       </c>
       <c r="M24" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N24" t="n">
         <v>0.296</v>
       </c>
       <c r="O24" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P24" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.675</v>
+        <v>0.677</v>
       </c>
       <c r="R24" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="S24" t="n">
         <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U24" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V24" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="W24" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="X24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
         <v>20.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.8</v>
+        <v>-11.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4761,40 +4828,40 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -4847,43 +4914,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
         <v>18</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>0.545</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J25" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L25" t="n">
         <v>10.1</v>
       </c>
       <c r="M25" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O25" t="n">
         <v>17.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0.8</v>
@@ -4892,43 +4959,43 @@
         <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="V25" t="n">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="W25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X25" t="n">
         <v>4.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z25" t="n">
         <v>22.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB25" t="n">
         <v>105.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
@@ -4937,19 +5004,19 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ25" t="n">
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
@@ -4958,10 +5025,10 @@
         <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -4973,13 +5040,13 @@
         <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
         <v>17</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -4994,13 +5061,13 @@
         <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>0.788</v>
+        <v>0.781</v>
       </c>
       <c r="H26" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J26" t="n">
-        <v>86.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L26" t="n">
         <v>10.1</v>
       </c>
       <c r="M26" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
         <v>15.4</v>
@@ -5068,37 +5135,37 @@
         <v>19.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="R26" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S26" t="n">
         <v>35.4</v>
       </c>
       <c r="T26" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V26" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y26" t="n">
         <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
         <v>104</v>
@@ -5107,7 +5174,7 @@
         <v>7.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,10 +5186,10 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
         <v>4</v>
@@ -5131,16 +5198,16 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
         <v>28</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5164,19 +5231,19 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
         <v>7</v>
@@ -5361,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -5396,34 +5463,34 @@
         <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="H28" t="n">
         <v>49.3</v>
       </c>
       <c r="I28" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>0.372</v>
+        <v>0.382</v>
       </c>
       <c r="O28" t="n">
         <v>17.5</v>
@@ -5432,7 +5499,7 @@
         <v>22.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
@@ -5444,13 +5511,13 @@
         <v>44.2</v>
       </c>
       <c r="U28" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W28" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>5.6</v>
@@ -5459,19 +5526,19 @@
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.4</v>
+        <v>102.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5486,22 +5553,22 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM28" t="n">
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5513,37 +5580,37 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
       </c>
       <c r="AU28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX28" t="n">
         <v>6</v>
       </c>
-      <c r="AV28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>4</v>
-      </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -5575,115 +5642,115 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.75</v>
+        <v>0.774</v>
       </c>
       <c r="H29" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
         <v>39.4</v>
       </c>
       <c r="J29" t="n">
-        <v>85.3</v>
+        <v>84.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
-        <v>0.363</v>
+        <v>0.368</v>
       </c>
       <c r="O29" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="P29" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
         <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T29" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="U29" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
       </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>108.1</v>
+        <v>108.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
         <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
       </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5695,7 +5762,7 @@
         <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5704,19 +5771,19 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY29" t="n">
         <v>22</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>23</v>
       </c>
       <c r="AZ29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
         <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>0.344</v>
+        <v>0.323</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J30" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O30" t="n">
         <v>17.6</v>
@@ -5796,19 +5863,19 @@
         <v>23.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R30" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S30" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T30" t="n">
         <v>41.9</v>
       </c>
       <c r="U30" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V30" t="n">
         <v>14.7</v>
@@ -5817,7 +5884,7 @@
         <v>6.2</v>
       </c>
       <c r="X30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y30" t="n">
         <v>4.7</v>
@@ -5826,37 +5893,37 @@
         <v>18.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB30" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.8</v>
+        <v>-4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
         <v>22</v>
       </c>
       <c r="AG30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>13</v>
@@ -5874,16 +5941,16 @@
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
@@ -5895,7 +5962,7 @@
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" t="n">
         <v>22</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.71</v>
+        <v>0.733</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.7</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L31" t="n">
         <v>6.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O31" t="n">
         <v>16.2</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.736</v>
+        <v>0.74</v>
       </c>
       <c r="R31" t="n">
         <v>10.6</v>
       </c>
       <c r="S31" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U31" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="V31" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="W31" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X31" t="n">
         <v>5</v>
@@ -6005,37 +6072,37 @@
         <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="AA31" t="n">
         <v>20.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.2</v>
+        <v>100.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI31" t="n">
         <v>7</v>
       </c>
-      <c r="AF31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>8</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6053,10 +6120,10 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
@@ -6071,10 +6138,10 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -6083,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-30-2014-15</t>
+          <t>2014-12-30</t>
         </is>
       </c>
     </row>
